--- a/pubs/2026 Pubs.xlsx
+++ b/pubs/2026 Pubs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\WebSite\pubs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C74E4F4-1FF3-404A-B971-0ACD6D7559CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1D9EFEC-A6A1-44BB-9CDC-EAC74ACC72A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="807" uniqueCount="349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="813" uniqueCount="352">
   <si>
     <t>London</t>
   </si>
@@ -1082,6 +1082,15 @@
   </si>
   <si>
     <t>Leros</t>
+  </si>
+  <si>
+    <t>Astypalaia</t>
+  </si>
+  <si>
+    <t>Ageri Restaurant</t>
+  </si>
+  <si>
+    <t>The Mills</t>
   </si>
 </sst>
 </file>
@@ -1649,7 +1658,7 @@
       </c>
       <c r="G4" s="12">
         <f>COUNTIF(Abroad!C:C, "&lt;&gt;") - 1</f>
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -1673,7 +1682,7 @@
       </c>
       <c r="G5" s="12">
         <f>G3+G4</f>
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -6850,83 +6859,107 @@
       <c r="A112" s="8">
         <v>111</v>
       </c>
-    </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B112" s="1">
+        <v>46278</v>
+      </c>
+      <c r="C112" t="s">
+        <v>351</v>
+      </c>
+      <c r="D112" t="s">
+        <v>349</v>
+      </c>
+      <c r="E112" s="2" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113" s="8">
         <v>112</v>
       </c>
-    </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B113" s="1">
+        <v>46278</v>
+      </c>
+      <c r="C113" t="s">
+        <v>350</v>
+      </c>
+      <c r="D113" t="s">
+        <v>349</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114" s="8">
         <v>113</v>
       </c>
     </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115" s="8">
         <v>114</v>
       </c>
     </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116" s="8">
         <v>115</v>
       </c>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117" s="8">
         <v>116</v>
       </c>
     </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A118" s="8">
         <v>117</v>
       </c>
     </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A119" s="8">
         <v>118</v>
       </c>
     </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A120" s="8">
         <v>119</v>
       </c>
     </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A121" s="8">
         <v>120</v>
       </c>
     </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A122" s="8">
         <v>121</v>
       </c>
     </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A123" s="8">
         <v>122</v>
       </c>
     </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A124" s="8">
         <v>123</v>
       </c>
     </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A125" s="8">
         <v>124</v>
       </c>
     </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A126" s="8">
         <v>125</v>
       </c>
     </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A127" s="8">
         <v>126</v>
       </c>
     </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A128" s="8">
         <v>127</v>
       </c>

--- a/pubs/2026 Pubs.xlsx
+++ b/pubs/2026 Pubs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\WebSite\pubs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1D9EFEC-A6A1-44BB-9CDC-EAC74ACC72A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB23BD5F-DBEE-473D-B41B-D350B94D4BE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="813" uniqueCount="352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="822" uniqueCount="356">
   <si>
     <t>London</t>
   </si>
@@ -1091,6 +1091,18 @@
   </si>
   <si>
     <t>The Mills</t>
+  </si>
+  <si>
+    <t>Lipsi</t>
+  </si>
+  <si>
+    <t>Manolis Tastes</t>
+  </si>
+  <si>
+    <t>Ouzerie Nick and Loulis</t>
+  </si>
+  <si>
+    <t>Ouzeri Sophocles</t>
   </si>
 </sst>
 </file>
@@ -1658,7 +1670,7 @@
       </c>
       <c r="G4" s="12">
         <f>COUNTIF(Abroad!C:C, "&lt;&gt;") - 1</f>
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -1682,7 +1694,7 @@
       </c>
       <c r="G5" s="12">
         <f>G3+G4</f>
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -6893,15 +6905,51 @@
       <c r="A114" s="8">
         <v>113</v>
       </c>
+      <c r="B114" s="1">
+        <v>46282</v>
+      </c>
+      <c r="C114" t="s">
+        <v>355</v>
+      </c>
+      <c r="D114" t="s">
+        <v>352</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>341</v>
+      </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115" s="8">
         <v>114</v>
       </c>
+      <c r="B115" s="1">
+        <v>46282</v>
+      </c>
+      <c r="C115" t="s">
+        <v>353</v>
+      </c>
+      <c r="D115" t="s">
+        <v>352</v>
+      </c>
+      <c r="E115" s="2" t="s">
+        <v>341</v>
+      </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116" s="8">
         <v>115</v>
+      </c>
+      <c r="B116" s="1">
+        <v>46282</v>
+      </c>
+      <c r="C116" t="s">
+        <v>354</v>
+      </c>
+      <c r="D116" t="s">
+        <v>352</v>
+      </c>
+      <c r="E116" s="2" t="s">
+        <v>341</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.3">

--- a/pubs/2026 Pubs.xlsx
+++ b/pubs/2026 Pubs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\WebSite\pubs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB23BD5F-DBEE-473D-B41B-D350B94D4BE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94BE0A7D-B9A2-41F2-93CD-DC2BD7219546}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="822" uniqueCount="356">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="825" uniqueCount="357">
   <si>
     <t>London</t>
   </si>
@@ -1103,6 +1103,9 @@
   </si>
   <si>
     <t>Ouzeri Sophocles</t>
+  </si>
+  <si>
+    <t>Platia Lipsi</t>
   </si>
 </sst>
 </file>
@@ -1670,7 +1673,7 @@
       </c>
       <c r="G4" s="12">
         <f>COUNTIF(Abroad!C:C, "&lt;&gt;") - 1</f>
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -1694,7 +1697,7 @@
       </c>
       <c r="G5" s="12">
         <f>G3+G4</f>
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -6956,6 +6959,18 @@
       <c r="A117" s="8">
         <v>116</v>
       </c>
+      <c r="B117" s="1">
+        <v>46283</v>
+      </c>
+      <c r="C117" t="s">
+        <v>356</v>
+      </c>
+      <c r="D117" t="s">
+        <v>352</v>
+      </c>
+      <c r="E117" s="2" t="s">
+        <v>341</v>
+      </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A118" s="8">

--- a/pubs/2026 Pubs.xlsx
+++ b/pubs/2026 Pubs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\WebSite\pubs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94BE0A7D-B9A2-41F2-93CD-DC2BD7219546}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38B1A990-0C0F-48F2-AA5C-1B8D4E08C0FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="825" uniqueCount="357">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="828" uniqueCount="358">
   <si>
     <t>London</t>
   </si>
@@ -1106,6 +1106,9 @@
   </si>
   <si>
     <t>Platia Lipsi</t>
+  </si>
+  <si>
+    <t>To Steki</t>
   </si>
 </sst>
 </file>
@@ -1673,7 +1676,7 @@
       </c>
       <c r="G4" s="12">
         <f>COUNTIF(Abroad!C:C, "&lt;&gt;") - 1</f>
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -1697,7 +1700,7 @@
       </c>
       <c r="G5" s="12">
         <f>G3+G4</f>
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -6976,6 +6979,18 @@
       <c r="A118" s="8">
         <v>117</v>
       </c>
+      <c r="B118" s="1">
+        <v>46288</v>
+      </c>
+      <c r="C118" t="s">
+        <v>357</v>
+      </c>
+      <c r="D118" t="s">
+        <v>348</v>
+      </c>
+      <c r="E118" s="2" t="s">
+        <v>341</v>
+      </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A119" s="8">

--- a/pubs/2026 Pubs.xlsx
+++ b/pubs/2026 Pubs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\WebSite\pubs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38B1A990-0C0F-48F2-AA5C-1B8D4E08C0FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D60C8BE-D929-4FEA-BDD7-355E671A908F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="828" uniqueCount="358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="831" uniqueCount="359">
   <si>
     <t>London</t>
   </si>
@@ -1109,6 +1109,9 @@
   </si>
   <si>
     <t>To Steki</t>
+  </si>
+  <si>
+    <t>Argo Taverna</t>
   </si>
 </sst>
 </file>
@@ -1676,7 +1679,7 @@
       </c>
       <c r="G4" s="12">
         <f>COUNTIF(Abroad!C:C, "&lt;&gt;") - 1</f>
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -1700,7 +1703,7 @@
       </c>
       <c r="G5" s="12">
         <f>G3+G4</f>
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -6996,6 +6999,18 @@
       <c r="A119" s="8">
         <v>118</v>
       </c>
+      <c r="B119" s="1">
+        <v>46290</v>
+      </c>
+      <c r="C119" t="s">
+        <v>358</v>
+      </c>
+      <c r="D119" t="s">
+        <v>348</v>
+      </c>
+      <c r="E119" s="2" t="s">
+        <v>341</v>
+      </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A120" s="8">

--- a/pubs/2026 Pubs.xlsx
+++ b/pubs/2026 Pubs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\WebSite\pubs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D60C8BE-D929-4FEA-BDD7-355E671A908F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D11CE550-D4F7-4AD3-B7B0-05ADA6559B15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="831" uniqueCount="359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="834" uniqueCount="360">
   <si>
     <t>London</t>
   </si>
@@ -1112,6 +1112,9 @@
   </si>
   <si>
     <t>Argo Taverna</t>
+  </si>
+  <si>
+    <t>Ta Kroupia</t>
   </si>
 </sst>
 </file>
@@ -1679,7 +1682,7 @@
       </c>
       <c r="G4" s="12">
         <f>COUNTIF(Abroad!C:C, "&lt;&gt;") - 1</f>
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -1703,7 +1706,7 @@
       </c>
       <c r="G5" s="12">
         <f>G3+G4</f>
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -7016,6 +7019,18 @@
       <c r="A120" s="8">
         <v>119</v>
       </c>
+      <c r="B120" s="1">
+        <v>46294</v>
+      </c>
+      <c r="C120" t="s">
+        <v>359</v>
+      </c>
+      <c r="D120" t="s">
+        <v>348</v>
+      </c>
+      <c r="E120" s="2" t="s">
+        <v>341</v>
+      </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A121" s="8">

--- a/pubs/2026 Pubs.xlsx
+++ b/pubs/2026 Pubs.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\WebSite\pubs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\WebSite\pubs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D11CE550-D4F7-4AD3-B7B0-05ADA6559B15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9EDF1FB-C3AC-4E64-AF1B-9A9D745AEDF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
   </bookViews>
   <sheets>
     <sheet name="UK" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="834" uniqueCount="360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="840" uniqueCount="362">
   <si>
     <t>London</t>
   </si>
@@ -1115,6 +1115,12 @@
   </si>
   <si>
     <t>Ta Kroupia</t>
+  </si>
+  <si>
+    <t>Theatre Bistro</t>
+  </si>
+  <si>
+    <t>Cow &amp; Cask</t>
   </si>
 </sst>
 </file>
@@ -1658,7 +1664,7 @@
       </c>
       <c r="G3" s="10">
         <f>COUNTIF(C:C, "&lt;&gt;") - 1</f>
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -1706,7 +1712,7 @@
       </c>
       <c r="G5" s="12">
         <f>G3+G4</f>
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -4474,10 +4480,34 @@
       <c r="A158" s="8">
         <v>157</v>
       </c>
+      <c r="B158" s="1">
+        <v>46305</v>
+      </c>
+      <c r="C158" t="s">
+        <v>360</v>
+      </c>
+      <c r="D158" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="E158" s="17" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A159" s="8">
         <v>158</v>
+      </c>
+      <c r="B159" s="1">
+        <v>46305</v>
+      </c>
+      <c r="C159" t="s">
+        <v>361</v>
+      </c>
+      <c r="D159" s="17" t="s">
+        <v>162</v>
+      </c>
+      <c r="E159" s="17" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.3">

--- a/pubs/2026 Pubs.xlsx
+++ b/pubs/2026 Pubs.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\WebSite\pubs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\WebSite\pubs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9EDF1FB-C3AC-4E64-AF1B-9A9D745AEDF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5097274-CE60-4B8C-9769-E8AE576DF9AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="840" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="852" uniqueCount="365">
   <si>
     <t>London</t>
   </si>
@@ -1121,6 +1121,15 @@
   </si>
   <si>
     <t>Cow &amp; Cask</t>
+  </si>
+  <si>
+    <t>The Shipwrights Arms</t>
+  </si>
+  <si>
+    <t>The Horseshoe</t>
+  </si>
+  <si>
+    <t>The Old Kings Head</t>
   </si>
 </sst>
 </file>
@@ -1664,7 +1673,7 @@
       </c>
       <c r="G3" s="10">
         <f>COUNTIF(C:C, "&lt;&gt;") - 1</f>
-        <v>158</v>
+        <v>162</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -1712,7 +1721,7 @@
       </c>
       <c r="G5" s="12">
         <f>G3+G4</f>
-        <v>277</v>
+        <v>281</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -4514,83 +4523,131 @@
       <c r="A160" s="8">
         <v>159</v>
       </c>
-    </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B160" s="1">
+        <v>46308</v>
+      </c>
+      <c r="C160" t="s">
+        <v>362</v>
+      </c>
+      <c r="D160" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="E160" s="17" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A161" s="8">
         <v>160</v>
       </c>
-    </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B161" s="1">
+        <v>46308</v>
+      </c>
+      <c r="C161" t="s">
+        <v>363</v>
+      </c>
+      <c r="D161" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="E161" s="17" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A162" s="8">
         <v>161</v>
       </c>
-    </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B162" s="1">
+        <v>46308</v>
+      </c>
+      <c r="C162" t="s">
+        <v>228</v>
+      </c>
+      <c r="D162" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="E162" s="17" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A163" s="8">
         <v>162</v>
       </c>
-    </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B163" s="1">
+        <v>46308</v>
+      </c>
+      <c r="C163" t="s">
+        <v>364</v>
+      </c>
+      <c r="D163" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="E163" s="17" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A164" s="8">
         <v>163</v>
       </c>
     </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A165" s="8">
         <v>164</v>
       </c>
     </row>
-    <row r="166" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A166" s="8">
         <v>165</v>
       </c>
     </row>
-    <row r="167" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A167" s="8">
         <v>166</v>
       </c>
     </row>
-    <row r="168" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A168" s="8">
         <v>167</v>
       </c>
     </row>
-    <row r="169" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A169" s="8">
         <v>168</v>
       </c>
     </row>
-    <row r="170" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A170" s="8">
         <v>169</v>
       </c>
     </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A171" s="8">
         <v>170</v>
       </c>
     </row>
-    <row r="172" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A172" s="8">
         <v>171</v>
       </c>
     </row>
-    <row r="173" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A173" s="8">
         <v>172</v>
       </c>
     </row>
-    <row r="174" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A174" s="8">
         <v>173</v>
       </c>
     </row>
-    <row r="175" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A175" s="8">
         <v>174</v>
       </c>
     </row>
-    <row r="176" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A176" s="8">
         <v>175</v>
       </c>

--- a/pubs/2026 Pubs.xlsx
+++ b/pubs/2026 Pubs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\WebSite\pubs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5097274-CE60-4B8C-9769-E8AE576DF9AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02A99D09-D2B4-4B0F-8054-35D3EC12CA84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
   </bookViews>
   <sheets>
     <sheet name="UK" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="852" uniqueCount="365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="873" uniqueCount="373">
   <si>
     <t>London</t>
   </si>
@@ -1130,6 +1130,30 @@
   </si>
   <si>
     <t>The Old Kings Head</t>
+  </si>
+  <si>
+    <t>Ibis bar</t>
+  </si>
+  <si>
+    <t>Café Infante</t>
+  </si>
+  <si>
+    <t>Quiosque de Leiria</t>
+  </si>
+  <si>
+    <t>Uzbek Kebab - Shisha Bar</t>
+  </si>
+  <si>
+    <t>Os Filipes Bar</t>
+  </si>
+  <si>
+    <t>El Desvan</t>
+  </si>
+  <si>
+    <t>Pastelaria Favo De Mel</t>
+  </si>
+  <si>
+    <t>Leiria</t>
   </si>
 </sst>
 </file>
@@ -1697,7 +1721,7 @@
       </c>
       <c r="G4" s="12">
         <f>COUNTIF(Abroad!C:C, "&lt;&gt;") - 1</f>
-        <v>119</v>
+        <v>126</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -1721,7 +1745,7 @@
       </c>
       <c r="G5" s="12">
         <f>G3+G4</f>
-        <v>281</v>
+        <v>288</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -7123,35 +7147,119 @@
       <c r="A121" s="8">
         <v>120</v>
       </c>
+      <c r="B121" s="1">
+        <v>46309</v>
+      </c>
+      <c r="C121" t="s">
+        <v>371</v>
+      </c>
+      <c r="D121" t="s">
+        <v>372</v>
+      </c>
+      <c r="E121" s="2" t="s">
+        <v>208</v>
+      </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A122" s="8">
         <v>121</v>
       </c>
+      <c r="B122" s="1">
+        <v>46310</v>
+      </c>
+      <c r="C122" t="s">
+        <v>365</v>
+      </c>
+      <c r="D122" t="s">
+        <v>372</v>
+      </c>
+      <c r="E122" s="2" t="s">
+        <v>208</v>
+      </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A123" s="8">
         <v>122</v>
       </c>
+      <c r="B123" s="1">
+        <v>46310</v>
+      </c>
+      <c r="C123" t="s">
+        <v>366</v>
+      </c>
+      <c r="D123" t="s">
+        <v>372</v>
+      </c>
+      <c r="E123" s="2" t="s">
+        <v>208</v>
+      </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A124" s="8">
         <v>123</v>
       </c>
+      <c r="B124" s="1">
+        <v>46310</v>
+      </c>
+      <c r="C124" t="s">
+        <v>367</v>
+      </c>
+      <c r="D124" t="s">
+        <v>372</v>
+      </c>
+      <c r="E124" s="2" t="s">
+        <v>208</v>
+      </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A125" s="8">
         <v>124</v>
       </c>
+      <c r="B125" s="1">
+        <v>46310</v>
+      </c>
+      <c r="C125" t="s">
+        <v>368</v>
+      </c>
+      <c r="D125" t="s">
+        <v>372</v>
+      </c>
+      <c r="E125" s="2" t="s">
+        <v>208</v>
+      </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A126" s="8">
         <v>125</v>
       </c>
+      <c r="B126" s="1">
+        <v>46310</v>
+      </c>
+      <c r="C126" t="s">
+        <v>369</v>
+      </c>
+      <c r="D126" t="s">
+        <v>372</v>
+      </c>
+      <c r="E126" s="2" t="s">
+        <v>208</v>
+      </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A127" s="8">
         <v>126</v>
+      </c>
+      <c r="B127" s="1">
+        <v>46310</v>
+      </c>
+      <c r="C127" t="s">
+        <v>370</v>
+      </c>
+      <c r="D127" t="s">
+        <v>372</v>
+      </c>
+      <c r="E127" s="2" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.3">

--- a/pubs/2026 Pubs.xlsx
+++ b/pubs/2026 Pubs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\WebSite\pubs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02A99D09-D2B4-4B0F-8054-35D3EC12CA84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0778B723-AA1D-4F53-85DA-8B41106A5452}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="873" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="876" uniqueCount="376">
   <si>
     <t>London</t>
   </si>
@@ -1154,6 +1154,15 @@
   </si>
   <si>
     <t>Leiria</t>
+  </si>
+  <si>
+    <t>Bar Cornobobò</t>
+  </si>
+  <si>
+    <t>Como</t>
+  </si>
+  <si>
+    <t>it</t>
   </si>
 </sst>
 </file>
@@ -1721,7 +1730,7 @@
       </c>
       <c r="G4" s="12">
         <f>COUNTIF(Abroad!C:C, "&lt;&gt;") - 1</f>
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -1745,7 +1754,7 @@
       </c>
       <c r="G5" s="12">
         <f>G3+G4</f>
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -7266,6 +7275,18 @@
       <c r="A128" s="8">
         <v>127</v>
       </c>
+      <c r="B128" s="1">
+        <v>46311</v>
+      </c>
+      <c r="C128" t="s">
+        <v>373</v>
+      </c>
+      <c r="D128" t="s">
+        <v>374</v>
+      </c>
+      <c r="E128" s="2" t="s">
+        <v>375</v>
+      </c>
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A129" s="8">

--- a/pubs/2026 Pubs.xlsx
+++ b/pubs/2026 Pubs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\WebSite\pubs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0778B723-AA1D-4F53-85DA-8B41106A5452}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{125700E0-EAD9-4FEE-92C6-AF1C79BB090A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="876" uniqueCount="376">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="885" uniqueCount="381">
   <si>
     <t>London</t>
   </si>
@@ -1163,6 +1163,21 @@
   </si>
   <si>
     <t>it</t>
+  </si>
+  <si>
+    <t>Löwenbräukeller</t>
+  </si>
+  <si>
+    <t>Higgins Ale Works</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Augustiner-Keller </t>
+  </si>
+  <si>
+    <t>Munich</t>
+  </si>
+  <si>
+    <t>de</t>
   </si>
 </sst>
 </file>
@@ -1730,7 +1745,7 @@
       </c>
       <c r="G4" s="12">
         <f>COUNTIF(Abroad!C:C, "&lt;&gt;") - 1</f>
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -1754,7 +1769,7 @@
       </c>
       <c r="G5" s="12">
         <f>G3+G4</f>
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -7288,82 +7303,118 @@
         <v>375</v>
       </c>
     </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A129" s="8">
         <v>128</v>
       </c>
-    </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B129" s="1">
+        <v>46313</v>
+      </c>
+      <c r="C129" t="s">
+        <v>376</v>
+      </c>
+      <c r="D129" t="s">
+        <v>379</v>
+      </c>
+      <c r="E129" s="2" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A130" s="8">
         <v>129</v>
       </c>
-    </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B130" s="1">
+        <v>46313</v>
+      </c>
+      <c r="C130" t="s">
+        <v>377</v>
+      </c>
+      <c r="D130" t="s">
+        <v>379</v>
+      </c>
+      <c r="E130" s="2" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A131" s="8">
         <v>130</v>
       </c>
-    </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B131" s="1">
+        <v>46313</v>
+      </c>
+      <c r="C131" t="s">
+        <v>378</v>
+      </c>
+      <c r="D131" t="s">
+        <v>379</v>
+      </c>
+      <c r="E131" s="2" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A132" s="8">
         <v>131</v>
       </c>
     </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A133" s="8">
         <v>132</v>
       </c>
     </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A134" s="8">
         <v>133</v>
       </c>
     </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A135" s="8">
         <v>134</v>
       </c>
     </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A136" s="8">
         <v>135</v>
       </c>
     </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A137" s="8">
         <v>136</v>
       </c>
     </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A138" s="8">
         <v>137</v>
       </c>
     </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A139" s="8">
         <v>138</v>
       </c>
     </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A140" s="8">
         <v>139</v>
       </c>
     </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A141" s="8">
         <v>140</v>
       </c>
     </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A142" s="8">
         <v>141</v>
       </c>
     </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A143" s="8">
         <v>142</v>
       </c>
     </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A144" s="8">
         <v>143</v>
       </c>

--- a/pubs/2026 Pubs.xlsx
+++ b/pubs/2026 Pubs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\WebSite\pubs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{125700E0-EAD9-4FEE-92C6-AF1C79BB090A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3206307B-645D-44D6-A7CA-2392738929FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="885" uniqueCount="381">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="897" uniqueCount="385">
   <si>
     <t>London</t>
   </si>
@@ -1178,6 +1178,18 @@
   </si>
   <si>
     <t>de</t>
+  </si>
+  <si>
+    <t>Chinesischer Turm</t>
+  </si>
+  <si>
+    <t>Hofbräuhaus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	Zum Stiftl Stehausschank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	Augustiner Stammhaus</t>
   </si>
 </sst>
 </file>
@@ -1745,7 +1757,7 @@
       </c>
       <c r="G4" s="12">
         <f>COUNTIF(Abroad!C:C, "&lt;&gt;") - 1</f>
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -1769,7 +1781,7 @@
       </c>
       <c r="G5" s="12">
         <f>G3+G4</f>
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -7358,20 +7370,68 @@
       <c r="A132" s="8">
         <v>131</v>
       </c>
+      <c r="B132" s="1">
+        <v>46314</v>
+      </c>
+      <c r="C132" t="s">
+        <v>381</v>
+      </c>
+      <c r="D132" t="s">
+        <v>379</v>
+      </c>
+      <c r="E132" s="2" t="s">
+        <v>380</v>
+      </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A133" s="8">
         <v>132</v>
       </c>
+      <c r="B133" s="1">
+        <v>46314</v>
+      </c>
+      <c r="C133" t="s">
+        <v>382</v>
+      </c>
+      <c r="D133" t="s">
+        <v>379</v>
+      </c>
+      <c r="E133" s="2" t="s">
+        <v>380</v>
+      </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A134" s="8">
         <v>133</v>
       </c>
+      <c r="B134" s="1">
+        <v>46314</v>
+      </c>
+      <c r="C134" t="s">
+        <v>383</v>
+      </c>
+      <c r="D134" t="s">
+        <v>379</v>
+      </c>
+      <c r="E134" s="2" t="s">
+        <v>380</v>
+      </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A135" s="8">
         <v>134</v>
+      </c>
+      <c r="B135" s="1">
+        <v>46314</v>
+      </c>
+      <c r="C135" t="s">
+        <v>384</v>
+      </c>
+      <c r="D135" t="s">
+        <v>379</v>
+      </c>
+      <c r="E135" s="2" t="s">
+        <v>380</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.3">

--- a/pubs/2026 Pubs.xlsx
+++ b/pubs/2026 Pubs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\WebSite\pubs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3206307B-645D-44D6-A7CA-2392738929FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E04C2654-7286-42B7-8F12-EA409822035A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="897" uniqueCount="385">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="921" uniqueCount="393">
   <si>
     <t>London</t>
   </si>
@@ -1190,6 +1190,30 @@
   </si>
   <si>
     <t xml:space="preserve">	Augustiner Stammhaus</t>
+  </si>
+  <si>
+    <t>Nuernberger Bratwurst Gloeckl am Dom</t>
+  </si>
+  <si>
+    <t>Biergarten Viktualienmarkt</t>
+  </si>
+  <si>
+    <t>Gasthaus Isarthor</t>
+  </si>
+  <si>
+    <t>Das Paulaner im Tal</t>
+  </si>
+  <si>
+    <t>Donisl</t>
+  </si>
+  <si>
+    <t>Schnitzelwirt im Spatenhof</t>
+  </si>
+  <si>
+    <t>Bavaria - Gaststätte und Restaurant</t>
+  </si>
+  <si>
+    <t>Augustiner Bräustuben</t>
   </si>
 </sst>
 </file>
@@ -1757,7 +1781,7 @@
       </c>
       <c r="G4" s="12">
         <f>COUNTIF(Abroad!C:C, "&lt;&gt;") - 1</f>
-        <v>134</v>
+        <v>142</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -1781,7 +1805,7 @@
       </c>
       <c r="G5" s="12">
         <f>G3+G4</f>
-        <v>296</v>
+        <v>304</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -7438,40 +7462,136 @@
       <c r="A136" s="8">
         <v>135</v>
       </c>
+      <c r="B136" s="1">
+        <v>46315</v>
+      </c>
+      <c r="C136" t="s">
+        <v>385</v>
+      </c>
+      <c r="D136" t="s">
+        <v>379</v>
+      </c>
+      <c r="E136" s="2" t="s">
+        <v>380</v>
+      </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A137" s="8">
         <v>136</v>
       </c>
+      <c r="B137" s="1">
+        <v>46315</v>
+      </c>
+      <c r="C137" t="s">
+        <v>386</v>
+      </c>
+      <c r="D137" t="s">
+        <v>379</v>
+      </c>
+      <c r="E137" s="2" t="s">
+        <v>380</v>
+      </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A138" s="8">
         <v>137</v>
       </c>
+      <c r="B138" s="1">
+        <v>46315</v>
+      </c>
+      <c r="C138" t="s">
+        <v>387</v>
+      </c>
+      <c r="D138" t="s">
+        <v>379</v>
+      </c>
+      <c r="E138" s="2" t="s">
+        <v>380</v>
+      </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A139" s="8">
         <v>138</v>
       </c>
+      <c r="B139" s="1">
+        <v>46315</v>
+      </c>
+      <c r="C139" t="s">
+        <v>388</v>
+      </c>
+      <c r="D139" t="s">
+        <v>379</v>
+      </c>
+      <c r="E139" s="2" t="s">
+        <v>380</v>
+      </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A140" s="8">
         <v>139</v>
       </c>
+      <c r="B140" s="1">
+        <v>46315</v>
+      </c>
+      <c r="C140" t="s">
+        <v>389</v>
+      </c>
+      <c r="D140" t="s">
+        <v>379</v>
+      </c>
+      <c r="E140" s="2" t="s">
+        <v>380</v>
+      </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A141" s="8">
         <v>140</v>
       </c>
+      <c r="B141" s="1">
+        <v>46315</v>
+      </c>
+      <c r="C141" t="s">
+        <v>390</v>
+      </c>
+      <c r="D141" t="s">
+        <v>379</v>
+      </c>
+      <c r="E141" s="2" t="s">
+        <v>380</v>
+      </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A142" s="8">
         <v>141</v>
       </c>
+      <c r="B142" s="1">
+        <v>46315</v>
+      </c>
+      <c r="C142" t="s">
+        <v>391</v>
+      </c>
+      <c r="D142" t="s">
+        <v>379</v>
+      </c>
+      <c r="E142" s="2" t="s">
+        <v>380</v>
+      </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A143" s="8">
         <v>142</v>
+      </c>
+      <c r="B143" s="1">
+        <v>46315</v>
+      </c>
+      <c r="C143" t="s">
+        <v>392</v>
+      </c>
+      <c r="D143" t="s">
+        <v>379</v>
+      </c>
+      <c r="E143" s="2" t="s">
+        <v>380</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.3">

--- a/pubs/2026 Pubs.xlsx
+++ b/pubs/2026 Pubs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\WebSite\pubs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E04C2654-7286-42B7-8F12-EA409822035A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33E79665-B7C8-454E-9B32-0D8AE08526B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="921" uniqueCount="393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="924" uniqueCount="394">
   <si>
     <t>London</t>
   </si>
@@ -1214,6 +1214,9 @@
   </si>
   <si>
     <t>Augustiner Bräustuben</t>
+  </si>
+  <si>
+    <t>Ibis Bar</t>
   </si>
 </sst>
 </file>
@@ -1781,7 +1784,7 @@
       </c>
       <c r="G4" s="12">
         <f>COUNTIF(Abroad!C:C, "&lt;&gt;") - 1</f>
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -1805,7 +1808,7 @@
       </c>
       <c r="G5" s="12">
         <f>G3+G4</f>
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -7395,10 +7398,10 @@
         <v>131</v>
       </c>
       <c r="B132" s="1">
-        <v>46314</v>
+        <v>46313</v>
       </c>
       <c r="C132" t="s">
-        <v>381</v>
+        <v>393</v>
       </c>
       <c r="D132" t="s">
         <v>379</v>
@@ -7415,7 +7418,7 @@
         <v>46314</v>
       </c>
       <c r="C133" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D133" t="s">
         <v>379</v>
@@ -7432,7 +7435,7 @@
         <v>46314</v>
       </c>
       <c r="C134" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D134" t="s">
         <v>379</v>
@@ -7449,7 +7452,7 @@
         <v>46314</v>
       </c>
       <c r="C135" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D135" t="s">
         <v>379</v>
@@ -7463,10 +7466,10 @@
         <v>135</v>
       </c>
       <c r="B136" s="1">
-        <v>46315</v>
+        <v>46314</v>
       </c>
       <c r="C136" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D136" t="s">
         <v>379</v>
@@ -7483,7 +7486,7 @@
         <v>46315</v>
       </c>
       <c r="C137" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D137" t="s">
         <v>379</v>
@@ -7500,7 +7503,7 @@
         <v>46315</v>
       </c>
       <c r="C138" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D138" t="s">
         <v>379</v>
@@ -7517,7 +7520,7 @@
         <v>46315</v>
       </c>
       <c r="C139" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D139" t="s">
         <v>379</v>
@@ -7534,7 +7537,7 @@
         <v>46315</v>
       </c>
       <c r="C140" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="D140" t="s">
         <v>379</v>
@@ -7551,7 +7554,7 @@
         <v>46315</v>
       </c>
       <c r="C141" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="D141" t="s">
         <v>379</v>
@@ -7568,7 +7571,7 @@
         <v>46315</v>
       </c>
       <c r="C142" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="D142" t="s">
         <v>379</v>
@@ -7585,7 +7588,7 @@
         <v>46315</v>
       </c>
       <c r="C143" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D143" t="s">
         <v>379</v>
@@ -7598,6 +7601,18 @@
       <c r="A144" s="8">
         <v>143</v>
       </c>
+      <c r="B144" s="1">
+        <v>46315</v>
+      </c>
+      <c r="C144" t="s">
+        <v>392</v>
+      </c>
+      <c r="D144" t="s">
+        <v>379</v>
+      </c>
+      <c r="E144" s="2" t="s">
+        <v>380</v>
+      </c>
     </row>
     <row r="145" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A145" s="8">
@@ -7863,12 +7878,12 @@
       <c r="A197" s="8">
         <v>196</v>
       </c>
-      <c r="E197"/>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A198" s="8">
         <v>197</v>
       </c>
+      <c r="E198"/>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A199" s="8">

--- a/pubs/2026 Pubs.xlsx
+++ b/pubs/2026 Pubs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\WebSite\pubs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33E79665-B7C8-454E-9B32-0D8AE08526B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C21F0B71-08AE-4130-9256-8EBFEBD175C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="924" uniqueCount="394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="930" uniqueCount="398">
   <si>
     <t>London</t>
   </si>
@@ -1217,6 +1217,18 @@
   </si>
   <si>
     <t>Ibis Bar</t>
+  </si>
+  <si>
+    <t>Pyšna Chałupa</t>
+  </si>
+  <si>
+    <t>Ministerstwo Browaru</t>
+  </si>
+  <si>
+    <t>Poznań</t>
+  </si>
+  <si>
+    <t>pl</t>
   </si>
 </sst>
 </file>
@@ -1784,7 +1796,7 @@
       </c>
       <c r="G4" s="12">
         <f>COUNTIF(Abroad!C:C, "&lt;&gt;") - 1</f>
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -1808,7 +1820,7 @@
       </c>
       <c r="G5" s="12">
         <f>G3+G4</f>
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -7614,82 +7626,106 @@
         <v>380</v>
       </c>
     </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A145" s="8">
         <v>144</v>
       </c>
-    </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B145" s="1">
+        <v>46317</v>
+      </c>
+      <c r="C145" t="s">
+        <v>394</v>
+      </c>
+      <c r="D145" t="s">
+        <v>396</v>
+      </c>
+      <c r="E145" s="2" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A146" s="8">
         <v>145</v>
       </c>
-    </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B146" s="1">
+        <v>46317</v>
+      </c>
+      <c r="C146" t="s">
+        <v>395</v>
+      </c>
+      <c r="D146" t="s">
+        <v>396</v>
+      </c>
+      <c r="E146" s="2" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A147" s="8">
         <v>146</v>
       </c>
     </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A148" s="8">
         <v>147</v>
       </c>
     </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A149" s="8">
         <v>148</v>
       </c>
     </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A150" s="8">
         <v>149</v>
       </c>
     </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A151" s="8">
         <v>150</v>
       </c>
     </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A152" s="8">
         <v>151</v>
       </c>
     </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A153" s="8">
         <v>152</v>
       </c>
     </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A154" s="8">
         <v>153</v>
       </c>
     </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A155" s="8">
         <v>154</v>
       </c>
     </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A156" s="8">
         <v>155</v>
       </c>
     </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A157" s="8">
         <v>156</v>
       </c>
     </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A158" s="8">
         <v>157</v>
       </c>
     </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A159" s="8">
         <v>158</v>
       </c>
     </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A160" s="8">
         <v>159</v>
       </c>

--- a/pubs/2026 Pubs.xlsx
+++ b/pubs/2026 Pubs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\WebSite\pubs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C21F0B71-08AE-4130-9256-8EBFEBD175C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4F9BAE2-3DFD-4D21-975E-43761679A4FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="930" uniqueCount="398">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="945" uniqueCount="402">
   <si>
     <t>London</t>
   </si>
@@ -1229,6 +1229,18 @@
   </si>
   <si>
     <t>pl</t>
+  </si>
+  <si>
+    <t>Silver Bar</t>
+  </si>
+  <si>
+    <t>Piwna Stopa</t>
+  </si>
+  <si>
+    <t>Pierogarnia Stary Młyn Poznań</t>
+  </si>
+  <si>
+    <t>Dom Piwa</t>
   </si>
 </sst>
 </file>
@@ -1796,7 +1808,7 @@
       </c>
       <c r="G4" s="12">
         <f>COUNTIF(Abroad!C:C, "&lt;&gt;") - 1</f>
-        <v>145</v>
+        <v>150</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -1820,7 +1832,7 @@
       </c>
       <c r="G5" s="12">
         <f>G3+G4</f>
-        <v>307</v>
+        <v>312</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -7664,25 +7676,85 @@
       <c r="A147" s="8">
         <v>146</v>
       </c>
+      <c r="B147" s="1">
+        <v>46317</v>
+      </c>
+      <c r="C147" t="s">
+        <v>398</v>
+      </c>
+      <c r="D147" t="s">
+        <v>396</v>
+      </c>
+      <c r="E147" s="2" t="s">
+        <v>397</v>
+      </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A148" s="8">
         <v>147</v>
       </c>
+      <c r="B148" s="1">
+        <v>46318</v>
+      </c>
+      <c r="C148" t="s">
+        <v>365</v>
+      </c>
+      <c r="D148" t="s">
+        <v>396</v>
+      </c>
+      <c r="E148" s="2" t="s">
+        <v>397</v>
+      </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A149" s="8">
         <v>148</v>
       </c>
+      <c r="B149" s="1">
+        <v>46318</v>
+      </c>
+      <c r="C149" t="s">
+        <v>399</v>
+      </c>
+      <c r="D149" t="s">
+        <v>396</v>
+      </c>
+      <c r="E149" s="2" t="s">
+        <v>397</v>
+      </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A150" s="8">
         <v>149</v>
       </c>
+      <c r="B150" s="1">
+        <v>46318</v>
+      </c>
+      <c r="C150" t="s">
+        <v>400</v>
+      </c>
+      <c r="D150" t="s">
+        <v>396</v>
+      </c>
+      <c r="E150" s="2" t="s">
+        <v>397</v>
+      </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A151" s="8">
         <v>150</v>
+      </c>
+      <c r="B151" s="1">
+        <v>46318</v>
+      </c>
+      <c r="C151" t="s">
+        <v>401</v>
+      </c>
+      <c r="D151" t="s">
+        <v>396</v>
+      </c>
+      <c r="E151" s="2" t="s">
+        <v>397</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.3">

--- a/pubs/2026 Pubs.xlsx
+++ b/pubs/2026 Pubs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\WebSite\pubs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4F9BAE2-3DFD-4D21-975E-43761679A4FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6548834F-349C-41B5-90D2-D3D4D526A3A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
   </bookViews>
   <sheets>
     <sheet name="UK" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="945" uniqueCount="402">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="954" uniqueCount="406">
   <si>
     <t>London</t>
   </si>
@@ -1241,6 +1241,18 @@
   </si>
   <si>
     <t>Dom Piwa</t>
+  </si>
+  <si>
+    <t>Pułapka Craft Beer &amp; Pizza</t>
+  </si>
+  <si>
+    <t>Labeerynt</t>
+  </si>
+  <si>
+    <t>Uwaga Piwo Piwna</t>
+  </si>
+  <si>
+    <t>Gdańsk</t>
   </si>
 </sst>
 </file>
@@ -1808,7 +1820,7 @@
       </c>
       <c r="G4" s="12">
         <f>COUNTIF(Abroad!C:C, "&lt;&gt;") - 1</f>
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -1832,7 +1844,7 @@
       </c>
       <c r="G5" s="12">
         <f>G3+G4</f>
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -7761,15 +7773,51 @@
       <c r="A152" s="8">
         <v>151</v>
       </c>
+      <c r="B152" s="1">
+        <v>46319</v>
+      </c>
+      <c r="C152" t="s">
+        <v>402</v>
+      </c>
+      <c r="D152" t="s">
+        <v>405</v>
+      </c>
+      <c r="E152" s="2" t="s">
+        <v>397</v>
+      </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A153" s="8">
         <v>152</v>
       </c>
+      <c r="B153" s="1">
+        <v>46319</v>
+      </c>
+      <c r="C153" t="s">
+        <v>403</v>
+      </c>
+      <c r="D153" t="s">
+        <v>405</v>
+      </c>
+      <c r="E153" s="2" t="s">
+        <v>397</v>
+      </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A154" s="8">
         <v>153</v>
+      </c>
+      <c r="B154" s="1">
+        <v>46319</v>
+      </c>
+      <c r="C154" t="s">
+        <v>404</v>
+      </c>
+      <c r="D154" t="s">
+        <v>405</v>
+      </c>
+      <c r="E154" s="2" t="s">
+        <v>397</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.3">

--- a/pubs/2026 Pubs.xlsx
+++ b/pubs/2026 Pubs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\WebSite\pubs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6548834F-349C-41B5-90D2-D3D4D526A3A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90122E7D-2A63-400D-BB7D-6A5836A3238A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{AA8581EE-2B0A-489C-80E8-4550A4BD8B73}"/>
   </bookViews>
   <sheets>
     <sheet name="UK" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="954" uniqueCount="406">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="969" uniqueCount="409">
   <si>
     <t>London</t>
   </si>
@@ -1237,9 +1237,6 @@
     <t>Piwna Stopa</t>
   </si>
   <si>
-    <t>Pierogarnia Stary Młyn Poznań</t>
-  </si>
-  <si>
     <t>Dom Piwa</t>
   </si>
   <si>
@@ -1253,6 +1250,18 @@
   </si>
   <si>
     <t>Gdańsk</t>
+  </si>
+  <si>
+    <t>Pierogarnia Stary Młyn</t>
+  </si>
+  <si>
+    <t>Mercure Bar</t>
+  </si>
+  <si>
+    <t>Grass Sports Bar</t>
+  </si>
+  <si>
+    <t>Browar &amp; Restauracja PG4</t>
   </si>
 </sst>
 </file>
@@ -1820,7 +1829,7 @@
       </c>
       <c r="G4" s="12">
         <f>COUNTIF(Abroad!C:C, "&lt;&gt;") - 1</f>
-        <v>153</v>
+        <v>158</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -1844,7 +1853,7 @@
       </c>
       <c r="G5" s="12">
         <f>G3+G4</f>
-        <v>315</v>
+        <v>320</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -7743,7 +7752,7 @@
         <v>46318</v>
       </c>
       <c r="C150" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="D150" t="s">
         <v>396</v>
@@ -7760,7 +7769,7 @@
         <v>46318</v>
       </c>
       <c r="C151" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D151" t="s">
         <v>396</v>
@@ -7777,10 +7786,10 @@
         <v>46319</v>
       </c>
       <c r="C152" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D152" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E152" s="2" t="s">
         <v>397</v>
@@ -7794,10 +7803,10 @@
         <v>46319</v>
       </c>
       <c r="C153" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="D153" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E153" s="2" t="s">
         <v>397</v>
@@ -7811,10 +7820,10 @@
         <v>46319</v>
       </c>
       <c r="C154" t="s">
+        <v>405</v>
+      </c>
+      <c r="D154" t="s">
         <v>404</v>
-      </c>
-      <c r="D154" t="s">
-        <v>405</v>
       </c>
       <c r="E154" s="2" t="s">
         <v>397</v>
@@ -7824,25 +7833,85 @@
       <c r="A155" s="8">
         <v>154</v>
       </c>
+      <c r="B155" s="1">
+        <v>46319</v>
+      </c>
+      <c r="C155" t="s">
+        <v>403</v>
+      </c>
+      <c r="D155" t="s">
+        <v>404</v>
+      </c>
+      <c r="E155" s="2" t="s">
+        <v>397</v>
+      </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A156" s="8">
         <v>155</v>
       </c>
+      <c r="B156" s="1">
+        <v>46320</v>
+      </c>
+      <c r="C156" t="s">
+        <v>406</v>
+      </c>
+      <c r="D156" t="s">
+        <v>404</v>
+      </c>
+      <c r="E156" s="2" t="s">
+        <v>397</v>
+      </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A157" s="8">
         <v>156</v>
       </c>
+      <c r="B157" s="1">
+        <v>46320</v>
+      </c>
+      <c r="C157" t="s">
+        <v>407</v>
+      </c>
+      <c r="D157" t="s">
+        <v>404</v>
+      </c>
+      <c r="E157" s="2" t="s">
+        <v>397</v>
+      </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A158" s="8">
         <v>157</v>
       </c>
+      <c r="B158" s="1">
+        <v>46320</v>
+      </c>
+      <c r="C158" t="s">
+        <v>405</v>
+      </c>
+      <c r="D158" t="s">
+        <v>404</v>
+      </c>
+      <c r="E158" s="2" t="s">
+        <v>397</v>
+      </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A159" s="8">
         <v>158</v>
+      </c>
+      <c r="B159" s="1">
+        <v>46320</v>
+      </c>
+      <c r="C159" t="s">
+        <v>408</v>
+      </c>
+      <c r="D159" t="s">
+        <v>404</v>
+      </c>
+      <c r="E159" s="2" t="s">
+        <v>397</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.3">
